--- a/tabtools/qa/output/tablex_numfmt_t8.xlsx
+++ b/tabtools/qa/output/tablex_numfmt_t8.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="112" uniqueCount="27">
   <si>
     <t>Cross Tab</t>
   </si>
@@ -100,10 +100,797 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="188">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
+  <fonts count="375">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <b/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11"/>
@@ -901,7 +1688,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="127">
+  <borders count="253">
     <border>
       <left/>
       <right/>
@@ -1767,11 +2554,869 @@
       <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
+    <border/>
+    <border/>
+    <border/>
+    <border/>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="thin"/>
+      <top style="none"/>
+      <bottom style="thin"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="253">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0"/>
@@ -2262,6 +3907,498 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="187" fillId="0" borderId="126" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="127" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="128" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="129" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="130" xfId="0"/>
+    <xf numFmtId="0" fontId="188" fillId="0" borderId="131" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="189" fillId="0" borderId="132" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="190" fillId="0" borderId="133" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="191" fillId="0" borderId="134" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="192" fillId="0" borderId="135" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="193" fillId="0" borderId="136" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="194" fillId="0" borderId="137" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="195" fillId="0" borderId="138" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="196" fillId="0" borderId="139" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="197" fillId="0" borderId="140" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="198" fillId="0" borderId="141" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="199" fillId="0" borderId="142" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="200" fillId="0" borderId="143" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="201" fillId="0" borderId="144" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="202" fillId="0" borderId="145" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="203" fillId="0" borderId="146" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="205" fillId="0" borderId="147" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="207" fillId="0" borderId="148" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="209" fillId="0" borderId="149" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="211" fillId="0" borderId="150" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="213" fillId="0" borderId="151" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="215" fillId="0" borderId="152" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="217" fillId="0" borderId="153" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="219" fillId="0" borderId="154" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="221" fillId="0" borderId="155" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="223" fillId="0" borderId="156" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="225" fillId="0" borderId="157" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="227" fillId="0" borderId="158" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="229" fillId="0" borderId="159" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="231" fillId="0" borderId="160" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="233" fillId="0" borderId="161" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="235" fillId="0" borderId="162" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="236" fillId="0" borderId="163" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="237" fillId="0" borderId="164" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="238" fillId="0" borderId="165" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="239" fillId="0" borderId="166" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="240" fillId="0" borderId="167" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="241" fillId="0" borderId="168" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="242" fillId="0" borderId="169" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="243" fillId="0" borderId="170" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="245" fillId="0" borderId="171" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="247" fillId="0" borderId="172" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="249" fillId="0" borderId="173" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="174" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="175" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="255" fillId="0" borderId="176" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="257" fillId="0" borderId="177" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="259" fillId="0" borderId="178" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="261" fillId="0" borderId="179" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="263" fillId="0" borderId="180" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="265" fillId="0" borderId="181" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="267" fillId="0" borderId="182" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="269" fillId="0" borderId="183" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="271" fillId="0" borderId="184" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="272" fillId="0" borderId="185" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="273" fillId="0" borderId="186" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="274" fillId="0" borderId="187" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="275" fillId="0" borderId="188" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="276" fillId="0" borderId="189" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="277" fillId="0" borderId="190" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="278" fillId="0" borderId="191" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="279" fillId="0" borderId="192" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="280" fillId="0" borderId="193" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="281" fillId="0" borderId="194" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="282" fillId="0" borderId="195" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="283" fillId="0" borderId="196" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="284" fillId="0" borderId="197" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="285" fillId="0" borderId="198" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="286" fillId="0" borderId="199" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="287" fillId="0" borderId="200" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="288" fillId="0" borderId="201" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="289" fillId="0" borderId="202" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="290" fillId="0" borderId="203" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="291" fillId="0" borderId="204" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="292" fillId="0" borderId="205" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="293" fillId="0" borderId="206" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="294" fillId="0" borderId="207" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="295" fillId="0" borderId="208" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="296" fillId="0" borderId="209" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="297" fillId="0" borderId="210" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="298" fillId="0" borderId="211" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="299" fillId="0" borderId="212" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="300" fillId="0" borderId="213" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="301" fillId="0" borderId="214" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="302" fillId="0" borderId="215" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="303" fillId="0" borderId="216" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="304" fillId="0" borderId="217" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="306" fillId="0" borderId="218" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="308" fillId="0" borderId="219" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="310" fillId="0" borderId="220" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="312" fillId="0" borderId="221" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="314" fillId="0" borderId="222" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="316" fillId="0" borderId="223" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="318" fillId="0" borderId="224" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="320" fillId="0" borderId="225" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="322" fillId="0" borderId="226" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="324" fillId="0" borderId="227" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="326" fillId="0" borderId="228" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="328" fillId="0" borderId="229" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="330" fillId="0" borderId="230" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="332" fillId="0" borderId="231" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="0" borderId="232" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="336" fillId="0" borderId="233" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="338" fillId="0" borderId="234" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="340" fillId="0" borderId="235" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="342" fillId="0" borderId="236" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="344" fillId="0" borderId="237" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="346" fillId="0" borderId="238" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="348" fillId="0" borderId="239" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="350" fillId="0" borderId="240" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="352" fillId="0" borderId="241" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="354" fillId="0" borderId="242" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="356" fillId="0" borderId="243" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="358" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="360" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="0" borderId="247" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="0" borderId="248" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="0" borderId="249" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="0" borderId="250" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="0" borderId="251" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="0" borderId="252" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2277,190 +4414,190 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="2" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" style="3" customWidth="true"/>
-    <col min="3" max="8" width="16.7109375" style="4" customWidth="true"/>
+    <col min="1" max="1" width="2.7109375" style="128" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" style="129" customWidth="true"/>
+    <col min="3" max="8" width="16.7109375" style="130" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="37" t="s">
+    <row r="1" s="127" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="163" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37" t="s">
+      <c r="B1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="163" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="193" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="194" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="69" t="s">
+      <c r="E2" s="195" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="196" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="71" t="s">
+      <c r="G2" s="197" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="205" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="92" t="s">
+      <c r="B3" s="218" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="93">
+      <c r="C3" s="219">
         <v>1</v>
       </c>
-      <c r="D3" s="94">
+      <c r="D3" s="220">
         <v>2</v>
       </c>
-      <c r="E3" s="95">
+      <c r="E3" s="221">
         <v>3</v>
       </c>
-      <c r="F3" s="96">
+      <c r="F3" s="222">
         <v>4</v>
       </c>
-      <c r="G3" s="97">
+      <c r="G3" s="223">
         <v>5</v>
       </c>
-      <c r="H3" s="98" t="s">
+      <c r="H3" s="224" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="225" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="100" t="s">
+      <c r="C4" s="226" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="101" t="s">
+      <c r="D4" s="227" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="229" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="104" t="s">
+      <c r="G4" s="230" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="105" t="s">
+      <c r="H4" s="231" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="106" t="s">
+      <c r="B5" s="232" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="107">
+      <c r="C5" s="233">
         <v>4564.5</v>
       </c>
-      <c r="D5" s="108">
+      <c r="D5" s="234">
         <v>5967.625</v>
       </c>
-      <c r="E5" s="109">
+      <c r="E5" s="235">
         <v>6607.0740740740739</v>
       </c>
-      <c r="F5" s="110">
+      <c r="F5" s="236">
         <v>5881.5555555555557</v>
       </c>
-      <c r="G5" s="111">
+      <c r="G5" s="237">
         <v>4204.5</v>
       </c>
-      <c r="H5" s="112">
+      <c r="H5" s="238">
         <v>6179.25</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="113" t="s">
+      <c r="B6" s="239" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="114" t="s">
+      <c r="C6" s="240" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="115" t="s">
+      <c r="D6" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="116">
+      <c r="E6" s="242">
         <v>4828.666666666667</v>
       </c>
-      <c r="F6" s="117">
+      <c r="F6" s="243">
         <v>6261.4444444444443</v>
       </c>
-      <c r="G6" s="118">
+      <c r="G6" s="244">
         <v>6292.666666666667</v>
       </c>
-      <c r="H6" s="119">
+      <c r="H6" s="245">
         <v>6070.1428571428569</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="120" t="s">
+      <c r="B7" s="246" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="121">
+      <c r="C7" s="247">
         <v>4564.5</v>
       </c>
-      <c r="D7" s="122">
+      <c r="D7" s="248">
         <v>5967.625</v>
       </c>
-      <c r="E7" s="123">
+      <c r="E7" s="249">
         <v>6429.2333333333336</v>
       </c>
-      <c r="F7" s="124">
+      <c r="F7" s="250">
         <v>6071.5</v>
       </c>
-      <c r="G7" s="125">
+      <c r="G7" s="251">
         <v>5913</v>
       </c>
-      <c r="H7" s="126">
+      <c r="H7" s="252">
         <v>6146.04347826087</v>
       </c>
     </row>
